--- a/Excel/MasterShortcut.xlsx
+++ b/Excel/MasterShortcut.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\DPBA_D2957\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A938DBC-34AE-427C-9795-AD4432332020}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4127F57D-EAE2-4337-9CDA-5C8882E3BBCC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="6" xr2:uid="{C8A82902-0894-4EF7-BF84-DAE301CCD016}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9580" windowHeight="2940" activeTab="3" xr2:uid="{C8A82902-0894-4EF7-BF84-DAE301CCD016}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex1" sheetId="1" r:id="rId1"/>
     <sheet name="Ex2" sheetId="2" r:id="rId2"/>
     <sheet name="Ex3" sheetId="3" r:id="rId3"/>
-    <sheet name="Ex4" sheetId="4" r:id="rId4"/>
-    <sheet name="Ex5" sheetId="5" r:id="rId5"/>
-    <sheet name="Ex6" sheetId="6" r:id="rId6"/>
-    <sheet name="NamedRanges" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId4"/>
+    <sheet name="Ex4" sheetId="4" r:id="rId5"/>
+    <sheet name="Ex5" sheetId="5" r:id="rId6"/>
+    <sheet name="Ex6" sheetId="6" r:id="rId7"/>
+    <sheet name="NamedRanges" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="191">
   <si>
     <t>Month</t>
   </si>
@@ -571,6 +572,39 @@
   </si>
   <si>
     <t>24:00AM</t>
+  </si>
+  <si>
+    <t>Sachin tendulkar</t>
+  </si>
+  <si>
+    <t>Virat kohli</t>
+  </si>
+  <si>
+    <t>Shah khan</t>
+  </si>
+  <si>
+    <t>Priyanka chopra</t>
+  </si>
+  <si>
+    <t>Deepika padukone</t>
+  </si>
+  <si>
+    <t>MS dhoni</t>
+  </si>
+  <si>
+    <t>Amitabh bachchan</t>
+  </si>
+  <si>
+    <t>Saina nehwal</t>
+  </si>
+  <si>
+    <t>Rohit sharma</t>
+  </si>
+  <si>
+    <t>Aishwarya rai</t>
+  </si>
+  <si>
+    <t>Ms Dhoni</t>
   </si>
 </sst>
 </file>
@@ -674,7 +708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -708,6 +742,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1726,6 +1762,237 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F013A94C-0167-4CEC-89A4-E3FD8830E2CB}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6328125" customWidth="1"/>
+    <col min="7" max="7" width="24.7265625" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="4" t="str">
+        <f>PROPER(F2)</f>
+        <v>Sachin Tendulkar</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="4" t="str">
+        <f>PROPER(F3)</f>
+        <v>Virat Kohli</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G4" s="4" t="str">
+        <f>PROPER(F4)</f>
+        <v>Shah Khan</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" s="4" t="str">
+        <f>PROPER(F5)</f>
+        <v>Priyanka Chopra</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="4" t="str">
+        <f>PROPER(F6)</f>
+        <v>Deepika Padukone</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="4" t="str">
+        <f>PROPER(F7)</f>
+        <v>Ms Dhoni</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f>PROPER(F8)</f>
+        <v>Amitabh Bachchan</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="4" t="str">
+        <f>PROPER(F9)</f>
+        <v>Saina Nehwal</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="4" t="str">
+        <f>PROPER(F10)</f>
+        <v>Rohit Sharma</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="4" t="str">
+        <f>PROPER(F11)</f>
+        <v>Aishwarya Rai</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E15">
+        <v>12000</v>
+      </c>
+      <c r="F15" t="str">
+        <f>TEXT(E15,"##,###")</f>
+        <v>12,000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E16" s="17"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E17" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7E3B67-D1D1-4A19-8783-97E98A4E99E1}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1854,7 +2121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34527972-2129-48AE-A7EE-BCE4F8D9217B}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2025,7 +2292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68F244A-C04B-4463-92D9-0F0AE3325918}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2196,7 +2463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B181B5B9-E1FE-48D8-A4C6-7E0C0D2B1D99}">
   <dimension ref="A2:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
